--- a/test/test-report-v1.1.0-beta1-result.xlsx
+++ b/test/test-report-v1.1.0-beta1-result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\HC Interaction 2026\c-six-\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AA0AA9-E609-4365-A205-AFC73A1E8F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D88D6C-717A-469F-A5F9-83133BD58CFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="950">
   <si>
     <t>SmartReport 测试报告</t>
   </si>
@@ -3079,18 +3079,18 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3406,122 +3406,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20"/>
     </row>
     <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
     </row>
     <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
     </row>
     <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -3574,16 +3574,16 @@
       <c r="C19" s="5"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -3641,60 +3641,55 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="20"/>
     </row>
     <row r="31" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B8:D8"/>
@@ -3706,6 +3701,11 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A29:H29"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8406,8 +8406,12 @@
       <c r="H111" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="I111" s="11"/>
-      <c r="J111" s="10"/>
+      <c r="I111" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J111" s="10" t="s">
+        <v>598</v>
+      </c>
       <c r="K111" s="10"/>
       <c r="L111" s="11"/>
       <c r="M111" s="11"/>
@@ -8439,8 +8443,12 @@
       <c r="H112" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="I112" s="11"/>
-      <c r="J112" s="10"/>
+      <c r="I112" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J112" s="10" t="s">
+        <v>603</v>
+      </c>
       <c r="K112" s="10"/>
       <c r="L112" s="11"/>
       <c r="M112" s="11"/>
@@ -8472,8 +8480,12 @@
       <c r="H113" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="I113" s="11"/>
-      <c r="J113" s="10"/>
+      <c r="I113" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J113" s="10" t="s">
+        <v>608</v>
+      </c>
       <c r="K113" s="10"/>
       <c r="L113" s="11"/>
       <c r="M113" s="11"/>
@@ -8505,8 +8517,12 @@
       <c r="H114" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="I114" s="11"/>
-      <c r="J114" s="10"/>
+      <c r="I114" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J114" s="10" t="s">
+        <v>612</v>
+      </c>
       <c r="K114" s="10"/>
       <c r="L114" s="11"/>
       <c r="M114" s="11"/>
@@ -8538,8 +8554,12 @@
       <c r="H115" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="I115" s="11"/>
-      <c r="J115" s="10"/>
+      <c r="I115" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J115" s="10" t="s">
+        <v>616</v>
+      </c>
       <c r="K115" s="10"/>
       <c r="L115" s="11"/>
       <c r="M115" s="11"/>
@@ -8571,8 +8591,12 @@
       <c r="H116" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="I116" s="11"/>
-      <c r="J116" s="10"/>
+      <c r="I116" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>621</v>
+      </c>
       <c r="K116" s="10"/>
       <c r="L116" s="11"/>
       <c r="M116" s="11"/>
@@ -8948,8 +8972,12 @@
       <c r="H125" s="10" t="s">
         <v>671</v>
       </c>
-      <c r="I125" s="11"/>
-      <c r="J125" s="10"/>
+      <c r="I125" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J125" s="10" t="s">
+        <v>671</v>
+      </c>
       <c r="K125" s="10"/>
       <c r="L125" s="11"/>
       <c r="M125" s="11"/>
@@ -8981,8 +9009,12 @@
       <c r="H126" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="I126" s="11"/>
-      <c r="J126" s="10"/>
+      <c r="I126" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="J126" s="10" t="s">
+        <v>675</v>
+      </c>
       <c r="K126" s="10"/>
       <c r="L126" s="11"/>
       <c r="M126" s="11"/>
